--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126986829</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>126986850</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126986825</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126986844</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126986811</v>
+        <v>126986854</v>
       </c>
       <c r="B6" t="n">
-        <v>91245</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712733</v>
+        <v>713078</v>
       </c>
       <c r="R6" t="n">
-        <v>7104319</v>
+        <v>7104061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126986854</v>
+        <v>126986811</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>91319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713078</v>
+        <v>712733</v>
       </c>
       <c r="R7" t="n">
-        <v>7104061</v>
+        <v>7104319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>126986846</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126986830</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>126986832</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>126986841</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>126986831</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,53 +1796,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126986818</v>
+        <v>126986849</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712755</v>
+        <v>713168</v>
       </c>
       <c r="R13" t="n">
-        <v>7104323</v>
+        <v>7104153</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,12 +1869,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1901,45 +1899,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126986849</v>
+        <v>126986818</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713168</v>
+        <v>712755</v>
       </c>
       <c r="R14" t="n">
-        <v>7104153</v>
+        <v>7104323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,18 +1980,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>126986838</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>126986836</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>126986833</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126986827</v>
+        <v>126986826</v>
       </c>
       <c r="B18" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,20 +2342,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712952</v>
+        <v>712914</v>
       </c>
       <c r="R18" t="n">
-        <v>7104173</v>
+        <v>7104222</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,10 +2416,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126986826</v>
+        <v>126986827</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,16 +2445,20 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712914</v>
+        <v>712952</v>
       </c>
       <c r="R19" t="n">
-        <v>7104222</v>
+        <v>7104173</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126986853</v>
+        <v>126986856</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>713144</v>
+        <v>712983</v>
       </c>
       <c r="R20" t="n">
-        <v>7104068</v>
+        <v>7104024</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,45 +2620,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986856</v>
+        <v>126986810</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>91677</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712983</v>
+        <v>712728</v>
       </c>
       <c r="R21" t="n">
-        <v>7104024</v>
+        <v>7104311</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,12 +2696,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera på samma låga</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2717,32 +2726,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126986835</v>
+        <v>126986809</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>58488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2752,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>713177</v>
+        <v>712748</v>
       </c>
       <c r="R22" t="n">
-        <v>7104176</v>
+        <v>7104315</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,18 +2799,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2820,10 +2823,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126986852</v>
+        <v>126986853</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2855,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>713128</v>
+        <v>713144</v>
       </c>
       <c r="R23" t="n">
-        <v>7104085</v>
+        <v>7104068</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2917,32 +2920,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126986809</v>
+        <v>126986835</v>
       </c>
       <c r="B24" t="n">
-        <v>58488</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2952,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712748</v>
+        <v>713177</v>
       </c>
       <c r="R24" t="n">
-        <v>7104315</v>
+        <v>7104176</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,12 +2993,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3014,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126986810</v>
+        <v>126986852</v>
       </c>
       <c r="B25" t="n">
-        <v>91603</v>
+        <v>98436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3025,37 +3034,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712728</v>
+        <v>713128</v>
       </c>
       <c r="R25" t="n">
-        <v>7104311</v>
+        <v>7104085</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3090,18 +3096,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Flera på samma låga</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>126986840</v>
       </c>
       <c r="B26" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>126986814</v>
       </c>
       <c r="B27" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>126986843</v>
       </c>
       <c r="B28" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3423,45 +3423,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126986821</v>
+        <v>126986828</v>
       </c>
       <c r="B29" t="n">
-        <v>97239</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>713031</v>
+        <v>713049</v>
       </c>
       <c r="R29" t="n">
-        <v>7104028</v>
+        <v>7104065</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3496,12 +3500,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3520,53 +3530,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126986817</v>
+        <v>126986821</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>97314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712853</v>
+        <v>713031</v>
       </c>
       <c r="R30" t="n">
-        <v>7104164</v>
+        <v>7104028</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3625,38 +3627,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126986828</v>
+        <v>126986817</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>57654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3664,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>713049</v>
+        <v>712853</v>
       </c>
       <c r="R31" t="n">
-        <v>7104065</v>
+        <v>7104164</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,18 +3708,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>126986848</v>
       </c>
       <c r="B32" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3835,57 +3835,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126987246</v>
+        <v>126986851</v>
       </c>
       <c r="B33" t="n">
-        <v>98382</v>
+        <v>98436</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712901</v>
+        <v>713073</v>
       </c>
       <c r="R33" t="n">
-        <v>7104242</v>
+        <v>7104248</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3926,7 +3914,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3945,45 +3932,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126986851</v>
+        <v>126987246</v>
       </c>
       <c r="B34" t="n">
-        <v>98361</v>
+        <v>98457</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>713073</v>
+        <v>712901</v>
       </c>
       <c r="R34" t="n">
-        <v>7104248</v>
+        <v>7104242</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4024,6 +4023,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>126986823</v>
       </c>
       <c r="B35" t="n">
-        <v>91446</v>
+        <v>91520</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4139,32 +4139,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126986842</v>
+        <v>126986808</v>
       </c>
       <c r="B36" t="n">
-        <v>98361</v>
+        <v>91284</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>713010</v>
+        <v>712922</v>
       </c>
       <c r="R36" t="n">
-        <v>7104171</v>
+        <v>7104137</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4212,18 +4212,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4245,7 +4239,7 @@
         <v>126986834</v>
       </c>
       <c r="B37" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4345,32 +4339,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126986808</v>
+        <v>126986842</v>
       </c>
       <c r="B38" t="n">
-        <v>91210</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4374,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712922</v>
+        <v>713010</v>
       </c>
       <c r="R38" t="n">
-        <v>7104137</v>
+        <v>7104171</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4418,12 +4412,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126986812</v>
+        <v>126986837</v>
       </c>
       <c r="B39" t="n">
-        <v>91245</v>
+        <v>98436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>713120</v>
+        <v>712883</v>
       </c>
       <c r="R39" t="n">
-        <v>7104213</v>
+        <v>7104261</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,12 +4515,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4539,32 +4545,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126986837</v>
+        <v>126986812</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>91319</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4574,10 +4580,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712883</v>
+        <v>713120</v>
       </c>
       <c r="R40" t="n">
-        <v>7104261</v>
+        <v>7104213</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4612,18 +4618,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986815</v>
+        <v>126986807</v>
       </c>
       <c r="B41" t="n">
-        <v>91245</v>
+        <v>91284</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713013</v>
+        <v>713191</v>
       </c>
       <c r="R41" t="n">
-        <v>7103963</v>
+        <v>7104098</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4739,32 +4739,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986845</v>
+        <v>126986815</v>
       </c>
       <c r="B42" t="n">
-        <v>98361</v>
+        <v>91319</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713090</v>
+        <v>713013</v>
       </c>
       <c r="R42" t="n">
-        <v>7104219</v>
+        <v>7103963</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,18 +4812,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4842,32 +4836,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986824</v>
+        <v>126986813</v>
       </c>
       <c r="B43" t="n">
-        <v>98361</v>
+        <v>91319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4877,10 +4871,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712932</v>
+        <v>713149</v>
       </c>
       <c r="R43" t="n">
-        <v>7104191</v>
+        <v>7104167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4915,18 +4909,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4945,32 +4933,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986813</v>
+        <v>126986845</v>
       </c>
       <c r="B44" t="n">
-        <v>91245</v>
+        <v>98436</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4980,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713149</v>
+        <v>713090</v>
       </c>
       <c r="R44" t="n">
-        <v>7104167</v>
+        <v>7104219</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5018,12 +5006,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5042,32 +5036,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986807</v>
+        <v>126986824</v>
       </c>
       <c r="B45" t="n">
-        <v>91210</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5077,10 +5071,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>713191</v>
+        <v>712932</v>
       </c>
       <c r="R45" t="n">
-        <v>7104098</v>
+        <v>7104191</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5115,12 +5109,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126986829</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>126986850</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126986825</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126986844</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126986854</v>
+        <v>126986811</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>91325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713078</v>
+        <v>712733</v>
       </c>
       <c r="R6" t="n">
-        <v>7104061</v>
+        <v>7104319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126986811</v>
+        <v>126986854</v>
       </c>
       <c r="B7" t="n">
-        <v>91319</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712733</v>
+        <v>713078</v>
       </c>
       <c r="R7" t="n">
-        <v>7104319</v>
+        <v>7104061</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>126986846</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126986830</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>126986832</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>126986841</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,45 +1693,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126986831</v>
+        <v>126986818</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712869</v>
+        <v>712755</v>
       </c>
       <c r="R12" t="n">
-        <v>7104253</v>
+        <v>7104323</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,18 +1774,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>5 bladosetter</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1796,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126986849</v>
+        <v>126986831</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1831,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713168</v>
+        <v>712869</v>
       </c>
       <c r="R13" t="n">
-        <v>7104153</v>
+        <v>7104253</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,7 +1873,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>5 bladosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,53 +1901,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126986818</v>
+        <v>126986849</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712755</v>
+        <v>713168</v>
       </c>
       <c r="R14" t="n">
-        <v>7104323</v>
+        <v>7104153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1980,12 +1974,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>126986838</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>126986836</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>126986833</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126986826</v>
+        <v>126986827</v>
       </c>
       <c r="B18" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,16 +2342,20 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712914</v>
+        <v>712952</v>
       </c>
       <c r="R18" t="n">
-        <v>7104222</v>
+        <v>7104173</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2416,10 +2420,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126986827</v>
+        <v>126986826</v>
       </c>
       <c r="B19" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,20 +2449,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712952</v>
+        <v>712914</v>
       </c>
       <c r="R19" t="n">
-        <v>7104173</v>
+        <v>7104222</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
         <v>126986856</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>126986810</v>
       </c>
       <c r="B21" t="n">
-        <v>91677</v>
+        <v>91683</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>126986853</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>126986835</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>126986852</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>126986840</v>
       </c>
       <c r="B26" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126986814</v>
+        <v>126986843</v>
       </c>
       <c r="B27" t="n">
-        <v>91319</v>
+        <v>98442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>713190</v>
+        <v>713017</v>
       </c>
       <c r="R27" t="n">
-        <v>7104098</v>
+        <v>7103987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,12 +3296,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>15 bladrosetter, 1 blomställning</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3320,32 +3326,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126986843</v>
+        <v>126986814</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>91325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3355,10 +3361,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>713017</v>
+        <v>713190</v>
       </c>
       <c r="R28" t="n">
-        <v>7103987</v>
+        <v>7104098</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,18 +3399,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>15 bladrosetter, 1 blomställning</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3423,49 +3423,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126986828</v>
+        <v>126986821</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>97320</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>713049</v>
+        <v>713031</v>
       </c>
       <c r="R29" t="n">
-        <v>7104065</v>
+        <v>7104028</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3500,18 +3496,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3530,45 +3520,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126986821</v>
+        <v>126986817</v>
       </c>
       <c r="B30" t="n">
-        <v>97314</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>713031</v>
+        <v>712853</v>
       </c>
       <c r="R30" t="n">
-        <v>7104028</v>
+        <v>7104164</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3627,42 +3625,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126986817</v>
+        <v>126986828</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3670,10 +3664,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712853</v>
+        <v>713049</v>
       </c>
       <c r="R31" t="n">
-        <v>7104164</v>
+        <v>7104065</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3708,12 +3702,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>126986848</v>
       </c>
       <c r="B32" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3835,45 +3835,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126986851</v>
+        <v>126987246</v>
       </c>
       <c r="B33" t="n">
-        <v>98436</v>
+        <v>98463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>713073</v>
+        <v>712901</v>
       </c>
       <c r="R33" t="n">
-        <v>7104248</v>
+        <v>7104242</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3914,6 +3926,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3932,57 +3945,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126987246</v>
+        <v>126986851</v>
       </c>
       <c r="B34" t="n">
-        <v>98457</v>
+        <v>98442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712901</v>
+        <v>713073</v>
       </c>
       <c r="R34" t="n">
-        <v>7104242</v>
+        <v>7104248</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4023,7 +4024,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>126986823</v>
       </c>
       <c r="B35" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>126986808</v>
       </c>
       <c r="B36" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4236,10 +4236,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126986834</v>
+        <v>126986842</v>
       </c>
       <c r="B37" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>713087</v>
+        <v>713010</v>
       </c>
       <c r="R37" t="n">
-        <v>7104233</v>
+        <v>7104171</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>30 bladrosetter</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4339,10 +4339,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126986842</v>
+        <v>126986834</v>
       </c>
       <c r="B38" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4374,10 +4374,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>713010</v>
+        <v>713087</v>
       </c>
       <c r="R38" t="n">
-        <v>7104171</v>
+        <v>7104233</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4445,7 +4445,7 @@
         <v>126986837</v>
       </c>
       <c r="B39" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>126986812</v>
       </c>
       <c r="B40" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986807</v>
+        <v>126986845</v>
       </c>
       <c r="B41" t="n">
-        <v>91284</v>
+        <v>98442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713191</v>
+        <v>713090</v>
       </c>
       <c r="R41" t="n">
-        <v>7104098</v>
+        <v>7104219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,12 +4715,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4739,32 +4745,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986815</v>
+        <v>126986807</v>
       </c>
       <c r="B42" t="n">
-        <v>91319</v>
+        <v>91290</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4774,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713013</v>
+        <v>713191</v>
       </c>
       <c r="R42" t="n">
-        <v>7103963</v>
+        <v>7104098</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4836,10 +4842,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986813</v>
+        <v>126986815</v>
       </c>
       <c r="B43" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4871,10 +4877,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713149</v>
+        <v>713013</v>
       </c>
       <c r="R43" t="n">
-        <v>7104167</v>
+        <v>7103963</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4933,32 +4939,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986845</v>
+        <v>126986813</v>
       </c>
       <c r="B44" t="n">
-        <v>98436</v>
+        <v>91325</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4974,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713090</v>
+        <v>713149</v>
       </c>
       <c r="R44" t="n">
-        <v>7104219</v>
+        <v>7104167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,18 +5012,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>126986824</v>
       </c>
       <c r="B45" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126986811</v>
+        <v>126986854</v>
       </c>
       <c r="B6" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712733</v>
+        <v>713078</v>
       </c>
       <c r="R6" t="n">
-        <v>7104319</v>
+        <v>7104061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126986854</v>
+        <v>126986811</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713078</v>
+        <v>712733</v>
       </c>
       <c r="R7" t="n">
-        <v>7104061</v>
+        <v>7104319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1693,53 +1693,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126986818</v>
+        <v>126986831</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712755</v>
+        <v>712869</v>
       </c>
       <c r="R12" t="n">
-        <v>7104323</v>
+        <v>7104253</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,12 +1766,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>5 bladosetter</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1798,7 +1796,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126986831</v>
+        <v>126986849</v>
       </c>
       <c r="B13" t="n">
         <v>98442</v>
@@ -1833,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712869</v>
+        <v>713168</v>
       </c>
       <c r="R13" t="n">
-        <v>7104253</v>
+        <v>7104153</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,7 +1871,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>5 bladosetter</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1901,45 +1899,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126986849</v>
+        <v>126986818</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713168</v>
+        <v>712755</v>
       </c>
       <c r="R14" t="n">
-        <v>7104153</v>
+        <v>7104323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,18 +1980,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126986856</v>
+        <v>126986809</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>58488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>208245</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712983</v>
+        <v>712748</v>
       </c>
       <c r="R20" t="n">
-        <v>7104024</v>
+        <v>7104315</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986810</v>
+        <v>126986853</v>
       </c>
       <c r="B21" t="n">
-        <v>91683</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,37 +2631,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712728</v>
+        <v>713144</v>
       </c>
       <c r="R21" t="n">
-        <v>7104311</v>
+        <v>7104068</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,18 +2693,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Flera på samma låga</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2726,32 +2717,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126986809</v>
+        <v>126986835</v>
       </c>
       <c r="B22" t="n">
-        <v>58488</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2761,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712748</v>
+        <v>713177</v>
       </c>
       <c r="R22" t="n">
-        <v>7104315</v>
+        <v>7104176</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2799,12 +2790,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2823,7 +2820,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126986853</v>
+        <v>126986852</v>
       </c>
       <c r="B23" t="n">
         <v>98442</v>
@@ -2858,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>713144</v>
+        <v>713128</v>
       </c>
       <c r="R23" t="n">
-        <v>7104068</v>
+        <v>7104085</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,7 +2917,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126986835</v>
+        <v>126986840</v>
       </c>
       <c r="B24" t="n">
         <v>98442</v>
@@ -2955,10 +2952,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>713177</v>
+        <v>713097</v>
       </c>
       <c r="R24" t="n">
-        <v>7104176</v>
+        <v>7104180</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2995,7 +2992,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>30 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3023,32 +3020,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126986852</v>
+        <v>126986856</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>713128</v>
+        <v>712983</v>
       </c>
       <c r="R25" t="n">
-        <v>7104085</v>
+        <v>7104024</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126986840</v>
+        <v>126986810</v>
       </c>
       <c r="B26" t="n">
-        <v>98442</v>
+        <v>91683</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,34 +3128,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>713097</v>
+        <v>712728</v>
       </c>
       <c r="R26" t="n">
-        <v>7104180</v>
+        <v>7104311</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>Flera på samma låga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,42 +3520,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126986817</v>
+        <v>126986828</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3563,10 +3559,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712853</v>
+        <v>713049</v>
       </c>
       <c r="R30" t="n">
-        <v>7104164</v>
+        <v>7104065</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,12 +3597,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3625,38 +3627,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126986828</v>
+        <v>126986817</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3664,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>713049</v>
+        <v>712853</v>
       </c>
       <c r="R31" t="n">
-        <v>7104065</v>
+        <v>7104164</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,18 +3708,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126986837</v>
+        <v>126986812</v>
       </c>
       <c r="B39" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712883</v>
+        <v>713120</v>
       </c>
       <c r="R39" t="n">
-        <v>7104261</v>
+        <v>7104213</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,18 +4515,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4545,32 +4539,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126986812</v>
+        <v>126986837</v>
       </c>
       <c r="B40" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4580,10 +4574,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>713120</v>
+        <v>712883</v>
       </c>
       <c r="R40" t="n">
-        <v>7104213</v>
+        <v>7104261</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,12 +4612,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986845</v>
+        <v>126986815</v>
       </c>
       <c r="B41" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713090</v>
+        <v>713013</v>
       </c>
       <c r="R41" t="n">
-        <v>7104219</v>
+        <v>7103963</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,18 +4715,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4745,32 +4739,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986807</v>
+        <v>126986813</v>
       </c>
       <c r="B42" t="n">
-        <v>91290</v>
+        <v>91325</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4774,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713191</v>
+        <v>713149</v>
       </c>
       <c r="R42" t="n">
-        <v>7104098</v>
+        <v>7104167</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4842,32 +4836,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986815</v>
+        <v>126986807</v>
       </c>
       <c r="B43" t="n">
-        <v>91325</v>
+        <v>91290</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4877,10 +4871,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713013</v>
+        <v>713191</v>
       </c>
       <c r="R43" t="n">
-        <v>7103963</v>
+        <v>7104098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4939,32 +4933,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986813</v>
+        <v>126986845</v>
       </c>
       <c r="B44" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4974,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713149</v>
+        <v>713090</v>
       </c>
       <c r="R44" t="n">
-        <v>7104167</v>
+        <v>7104219</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5012,12 +5006,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126986843</v>
+        <v>126986814</v>
       </c>
       <c r="B27" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>713017</v>
+        <v>713190</v>
       </c>
       <c r="R27" t="n">
-        <v>7103987</v>
+        <v>7104098</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,18 +3296,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>15 bladrosetter, 1 blomställning</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3326,32 +3320,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126986814</v>
+        <v>126986843</v>
       </c>
       <c r="B28" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3361,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>713190</v>
+        <v>713017</v>
       </c>
       <c r="R28" t="n">
-        <v>7104098</v>
+        <v>7103987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,12 +3393,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>15 bladrosetter, 1 blomställning</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126986829</v>
+        <v>126986850</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713038</v>
+        <v>713205</v>
       </c>
       <c r="R2" t="n">
-        <v>7104070</v>
+        <v>7104125</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126986850</v>
+        <v>126986829</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713205</v>
+        <v>713038</v>
       </c>
       <c r="R3" t="n">
-        <v>7104125</v>
+        <v>7104070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,7 +853,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
         <v>126986825</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126986844</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>126986811</v>
       </c>
       <c r="B7" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126986846</v>
+        <v>126986830</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712967</v>
+        <v>713170</v>
       </c>
       <c r="R8" t="n">
-        <v>7104174</v>
+        <v>7104136</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>5 bladrosetter, 2 blomställningar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126986830</v>
+        <v>126986846</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713170</v>
+        <v>712967</v>
       </c>
       <c r="R9" t="n">
-        <v>7104136</v>
+        <v>7104174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>5 bladrosetter, 2 blomställningar</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,7 +1490,7 @@
         <v>126986832</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>126986841</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,45 +1693,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126986831</v>
+        <v>126986818</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712869</v>
+        <v>712755</v>
       </c>
       <c r="R12" t="n">
-        <v>7104253</v>
+        <v>7104323</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,18 +1774,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>5 bladosetter</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1796,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126986849</v>
+        <v>126986831</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1831,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713168</v>
+        <v>712869</v>
       </c>
       <c r="R13" t="n">
-        <v>7104153</v>
+        <v>7104253</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,7 +1873,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>5 bladosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,53 +1901,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126986818</v>
+        <v>126986849</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712755</v>
+        <v>713168</v>
       </c>
       <c r="R14" t="n">
-        <v>7104323</v>
+        <v>7104153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1980,12 +1974,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>126986838</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>126986836</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126986833</v>
+        <v>126986827</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,16 +2239,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712891</v>
+        <v>712952</v>
       </c>
       <c r="R17" t="n">
-        <v>7104145</v>
+        <v>7104173</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2285,7 +2289,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>30 bladrosetter, 1 blomställning</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2313,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126986827</v>
+        <v>126986826</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,20 +2346,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712952</v>
+        <v>712914</v>
       </c>
       <c r="R18" t="n">
-        <v>7104173</v>
+        <v>7104222</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,10 +2420,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126986826</v>
+        <v>126986833</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712914</v>
+        <v>712891</v>
       </c>
       <c r="R19" t="n">
-        <v>7104222</v>
+        <v>7104145</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>30 bladrosetter, 1 blomställning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2523,32 +2523,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126986809</v>
+        <v>126986856</v>
       </c>
       <c r="B20" t="n">
-        <v>58488</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208245</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712748</v>
+        <v>712983</v>
       </c>
       <c r="R20" t="n">
-        <v>7104315</v>
+        <v>7104024</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986853</v>
+        <v>126986810</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>91684</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,34 +2631,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>713144</v>
+        <v>712728</v>
       </c>
       <c r="R21" t="n">
-        <v>7104068</v>
+        <v>7104311</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,12 +2696,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera på samma låga</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2717,32 +2726,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126986835</v>
+        <v>126986809</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>58488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2752,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>713177</v>
+        <v>712748</v>
       </c>
       <c r="R22" t="n">
-        <v>7104176</v>
+        <v>7104315</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,18 +2799,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2820,10 +2823,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126986852</v>
+        <v>126986835</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2855,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>713128</v>
+        <v>713177</v>
       </c>
       <c r="R23" t="n">
-        <v>7104085</v>
+        <v>7104176</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,12 +2896,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2920,7 +2929,7 @@
         <v>126986840</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3020,32 +3029,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126986856</v>
+        <v>126986853</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3055,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712983</v>
+        <v>713144</v>
       </c>
       <c r="R25" t="n">
-        <v>7104024</v>
+        <v>7104068</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,10 +3126,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126986810</v>
+        <v>126986852</v>
       </c>
       <c r="B26" t="n">
-        <v>91683</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3128,37 +3137,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712728</v>
+        <v>713128</v>
       </c>
       <c r="R26" t="n">
-        <v>7104311</v>
+        <v>7104085</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,18 +3199,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Flera på samma låga</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126986814</v>
+        <v>126986843</v>
       </c>
       <c r="B27" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>713190</v>
+        <v>713017</v>
       </c>
       <c r="R27" t="n">
-        <v>7104098</v>
+        <v>7103987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,12 +3296,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>15 bladrosetter, 1 blomställning</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3320,32 +3326,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126986843</v>
+        <v>126986814</v>
       </c>
       <c r="B28" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3355,10 +3361,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>713017</v>
+        <v>713190</v>
       </c>
       <c r="R28" t="n">
-        <v>7103987</v>
+        <v>7104098</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,18 +3399,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>15 bladrosetter, 1 blomställning</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3423,45 +3423,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126986821</v>
+        <v>126986817</v>
       </c>
       <c r="B29" t="n">
-        <v>97320</v>
+        <v>57654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>713031</v>
+        <v>712853</v>
       </c>
       <c r="R29" t="n">
-        <v>7104028</v>
+        <v>7104164</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3523,7 +3531,7 @@
         <v>126986828</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3627,53 +3635,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126986817</v>
+        <v>126986821</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>97321</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712853</v>
+        <v>713031</v>
       </c>
       <c r="R31" t="n">
-        <v>7104164</v>
+        <v>7104028</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
         <v>126986848</v>
       </c>
       <c r="B32" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3835,57 +3835,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126987246</v>
+        <v>126986851</v>
       </c>
       <c r="B33" t="n">
-        <v>98463</v>
+        <v>98443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712901</v>
+        <v>713073</v>
       </c>
       <c r="R33" t="n">
-        <v>7104242</v>
+        <v>7104248</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3926,7 +3914,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3945,45 +3932,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126986851</v>
+        <v>126987246</v>
       </c>
       <c r="B34" t="n">
-        <v>98442</v>
+        <v>98464</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>713073</v>
+        <v>712901</v>
       </c>
       <c r="R34" t="n">
-        <v>7104248</v>
+        <v>7104242</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4024,6 +4023,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>126986823</v>
       </c>
       <c r="B35" t="n">
-        <v>91526</v>
+        <v>91527</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4139,32 +4139,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126986808</v>
+        <v>126986842</v>
       </c>
       <c r="B36" t="n">
-        <v>91290</v>
+        <v>98443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712922</v>
+        <v>713010</v>
       </c>
       <c r="R36" t="n">
-        <v>7104137</v>
+        <v>7104171</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4212,12 +4212,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4236,10 +4242,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126986842</v>
+        <v>126986834</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4271,10 +4277,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>713010</v>
+        <v>713087</v>
       </c>
       <c r="R37" t="n">
-        <v>7104171</v>
+        <v>7104233</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4311,7 +4317,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4339,32 +4345,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126986834</v>
+        <v>126986808</v>
       </c>
       <c r="B38" t="n">
-        <v>98442</v>
+        <v>91291</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4374,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>713087</v>
+        <v>712922</v>
       </c>
       <c r="R38" t="n">
-        <v>7104233</v>
+        <v>7104137</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4412,18 +4418,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126986812</v>
+        <v>126986837</v>
       </c>
       <c r="B39" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>713120</v>
+        <v>712883</v>
       </c>
       <c r="R39" t="n">
-        <v>7104213</v>
+        <v>7104261</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,12 +4515,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4539,32 +4545,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126986837</v>
+        <v>126986812</v>
       </c>
       <c r="B40" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4574,10 +4580,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712883</v>
+        <v>713120</v>
       </c>
       <c r="R40" t="n">
-        <v>7104261</v>
+        <v>7104213</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4612,18 +4618,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986815</v>
+        <v>126986845</v>
       </c>
       <c r="B41" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713013</v>
+        <v>713090</v>
       </c>
       <c r="R41" t="n">
-        <v>7103963</v>
+        <v>7104219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,12 +4715,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4739,32 +4745,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986813</v>
+        <v>126986824</v>
       </c>
       <c r="B42" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4774,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713149</v>
+        <v>712932</v>
       </c>
       <c r="R42" t="n">
-        <v>7104167</v>
+        <v>7104191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,12 +4818,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4839,7 +4851,7 @@
         <v>126986807</v>
       </c>
       <c r="B43" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4933,32 +4945,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986845</v>
+        <v>126986815</v>
       </c>
       <c r="B44" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4980,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713090</v>
+        <v>713013</v>
       </c>
       <c r="R44" t="n">
-        <v>7104219</v>
+        <v>7103963</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,18 +5018,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5036,32 +5042,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986824</v>
+        <v>126986813</v>
       </c>
       <c r="B45" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5071,10 +5077,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712932</v>
+        <v>713149</v>
       </c>
       <c r="R45" t="n">
-        <v>7104191</v>
+        <v>7104167</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5109,18 +5115,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126986850</v>
+        <v>126986829</v>
       </c>
       <c r="B2" t="n">
         <v>98443</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713205</v>
+        <v>713038</v>
       </c>
       <c r="R2" t="n">
-        <v>7104125</v>
+        <v>7104070</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +778,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126986829</v>
+        <v>126986850</v>
       </c>
       <c r="B3" t="n">
         <v>98443</v>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713038</v>
+        <v>713205</v>
       </c>
       <c r="R3" t="n">
-        <v>7104070</v>
+        <v>7104125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,7 +853,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1281,7 +1281,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126986830</v>
+        <v>126986846</v>
       </c>
       <c r="B8" t="n">
         <v>98443</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713170</v>
+        <v>712967</v>
       </c>
       <c r="R8" t="n">
-        <v>7104136</v>
+        <v>7104174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>5 bladrosetter, 2 blomställningar</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,7 +1384,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126986846</v>
+        <v>126986830</v>
       </c>
       <c r="B9" t="n">
         <v>98443</v>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712967</v>
+        <v>713170</v>
       </c>
       <c r="R9" t="n">
-        <v>7104174</v>
+        <v>7104136</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>5 bladrosetter, 2 blomställningar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3423,42 +3423,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126986817</v>
+        <v>126986828</v>
       </c>
       <c r="B29" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3466,10 +3462,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712853</v>
+        <v>713049</v>
       </c>
       <c r="R29" t="n">
-        <v>7104164</v>
+        <v>7104065</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3504,12 +3500,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3528,49 +3530,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126986828</v>
+        <v>126986821</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>97321</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>713049</v>
+        <v>713031</v>
       </c>
       <c r="R30" t="n">
-        <v>7104065</v>
+        <v>7104028</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3605,18 +3603,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3635,45 +3627,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126986821</v>
+        <v>126986817</v>
       </c>
       <c r="B31" t="n">
-        <v>97321</v>
+        <v>57654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>713031</v>
+        <v>712853</v>
       </c>
       <c r="R31" t="n">
-        <v>7104028</v>
+        <v>7104164</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3835,45 +3835,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126986851</v>
+        <v>126987246</v>
       </c>
       <c r="B33" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>713073</v>
+        <v>712901</v>
       </c>
       <c r="R33" t="n">
-        <v>7104248</v>
+        <v>7104242</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3914,6 +3926,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3932,57 +3945,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126987246</v>
+        <v>126986851</v>
       </c>
       <c r="B34" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712901</v>
+        <v>713073</v>
       </c>
       <c r="R34" t="n">
-        <v>7104242</v>
+        <v>7104248</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4023,7 +4024,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986845</v>
+        <v>126986807</v>
       </c>
       <c r="B41" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713090</v>
+        <v>713191</v>
       </c>
       <c r="R41" t="n">
-        <v>7104219</v>
+        <v>7104098</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,18 +4715,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4745,32 +4739,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986824</v>
+        <v>126986815</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4774,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712932</v>
+        <v>713013</v>
       </c>
       <c r="R42" t="n">
-        <v>7104191</v>
+        <v>7103963</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4818,18 +4812,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4848,32 +4836,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986807</v>
+        <v>126986813</v>
       </c>
       <c r="B43" t="n">
-        <v>91291</v>
+        <v>91326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4883,10 +4871,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713191</v>
+        <v>713149</v>
       </c>
       <c r="R43" t="n">
-        <v>7104098</v>
+        <v>7104167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4945,32 +4933,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986815</v>
+        <v>126986845</v>
       </c>
       <c r="B44" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4980,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713013</v>
+        <v>713090</v>
       </c>
       <c r="R44" t="n">
-        <v>7103963</v>
+        <v>7104219</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5018,12 +5006,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5042,32 +5036,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986813</v>
+        <v>126986824</v>
       </c>
       <c r="B45" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5077,10 +5071,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>713149</v>
+        <v>712932</v>
       </c>
       <c r="R45" t="n">
-        <v>7104167</v>
+        <v>7104191</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5115,12 +5109,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126986854</v>
+        <v>126986811</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713078</v>
+        <v>712733</v>
       </c>
       <c r="R6" t="n">
-        <v>7104061</v>
+        <v>7104319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126986811</v>
+        <v>126986854</v>
       </c>
       <c r="B7" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712733</v>
+        <v>713078</v>
       </c>
       <c r="R7" t="n">
-        <v>7104319</v>
+        <v>7104061</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126986826</v>
+        <v>126986833</v>
       </c>
       <c r="B18" t="n">
         <v>98443</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712914</v>
+        <v>712891</v>
       </c>
       <c r="R18" t="n">
-        <v>7104222</v>
+        <v>7104145</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>30 bladrosetter, 1 blomställning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2420,7 +2420,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126986833</v>
+        <v>126986826</v>
       </c>
       <c r="B19" t="n">
         <v>98443</v>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712891</v>
+        <v>712914</v>
       </c>
       <c r="R19" t="n">
-        <v>7104145</v>
+        <v>7104222</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>30 bladrosetter, 1 blomställning</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2523,32 +2523,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126986856</v>
+        <v>126986809</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>58488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>208245</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712983</v>
+        <v>712748</v>
       </c>
       <c r="R20" t="n">
-        <v>7104024</v>
+        <v>7104315</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986810</v>
+        <v>126986853</v>
       </c>
       <c r="B21" t="n">
-        <v>91684</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,37 +2631,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712728</v>
+        <v>713144</v>
       </c>
       <c r="R21" t="n">
-        <v>7104311</v>
+        <v>7104068</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,18 +2693,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Flera på samma låga</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2726,32 +2717,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126986809</v>
+        <v>126986835</v>
       </c>
       <c r="B22" t="n">
-        <v>58488</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2761,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712748</v>
+        <v>713177</v>
       </c>
       <c r="R22" t="n">
-        <v>7104315</v>
+        <v>7104176</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2799,12 +2790,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2823,7 +2820,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126986835</v>
+        <v>126986852</v>
       </c>
       <c r="B23" t="n">
         <v>98443</v>
@@ -2858,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>713177</v>
+        <v>713128</v>
       </c>
       <c r="R23" t="n">
-        <v>7104176</v>
+        <v>7104085</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2896,18 +2893,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3029,10 +3020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126986853</v>
+        <v>126986810</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>91684</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3040,34 +3031,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>713144</v>
+        <v>712728</v>
       </c>
       <c r="R25" t="n">
-        <v>7104068</v>
+        <v>7104311</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3102,12 +3096,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Flera på samma låga</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3126,32 +3126,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126986852</v>
+        <v>126986856</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>713128</v>
+        <v>712983</v>
       </c>
       <c r="R26" t="n">
-        <v>7104085</v>
+        <v>7104024</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3423,38 +3423,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126986828</v>
+        <v>126986817</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3462,10 +3466,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>713049</v>
+        <v>712853</v>
       </c>
       <c r="R29" t="n">
-        <v>7104065</v>
+        <v>7104164</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3500,18 +3504,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3530,45 +3528,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126986821</v>
+        <v>126986828</v>
       </c>
       <c r="B30" t="n">
-        <v>97321</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>713031</v>
+        <v>713049</v>
       </c>
       <c r="R30" t="n">
-        <v>7104028</v>
+        <v>7104065</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3603,12 +3605,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3627,53 +3635,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126986817</v>
+        <v>126986821</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>97321</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712853</v>
+        <v>713031</v>
       </c>
       <c r="R31" t="n">
-        <v>7104164</v>
+        <v>7104028</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3835,57 +3835,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126987246</v>
+        <v>126986851</v>
       </c>
       <c r="B33" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712901</v>
+        <v>713073</v>
       </c>
       <c r="R33" t="n">
-        <v>7104242</v>
+        <v>7104248</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3926,7 +3914,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3945,45 +3932,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126986851</v>
+        <v>126987246</v>
       </c>
       <c r="B34" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>713073</v>
+        <v>712901</v>
       </c>
       <c r="R34" t="n">
-        <v>7104248</v>
+        <v>7104242</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4024,6 +4023,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4139,32 +4139,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126986842</v>
+        <v>126986808</v>
       </c>
       <c r="B36" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>713010</v>
+        <v>712922</v>
       </c>
       <c r="R36" t="n">
-        <v>7104171</v>
+        <v>7104137</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4212,18 +4212,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4242,7 +4236,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126986834</v>
+        <v>126986842</v>
       </c>
       <c r="B37" t="n">
         <v>98443</v>
@@ -4277,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>713087</v>
+        <v>713010</v>
       </c>
       <c r="R37" t="n">
-        <v>7104233</v>
+        <v>7104171</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,7 +4311,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>30 bladrosetter</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4345,32 +4339,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126986808</v>
+        <v>126986834</v>
       </c>
       <c r="B38" t="n">
-        <v>91291</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4374,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712922</v>
+        <v>713087</v>
       </c>
       <c r="R38" t="n">
-        <v>7104137</v>
+        <v>7104233</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4418,12 +4412,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986807</v>
+        <v>126986815</v>
       </c>
       <c r="B41" t="n">
-        <v>91291</v>
+        <v>91326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713191</v>
+        <v>713013</v>
       </c>
       <c r="R41" t="n">
-        <v>7104098</v>
+        <v>7103963</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4739,32 +4739,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986815</v>
+        <v>126986845</v>
       </c>
       <c r="B42" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713013</v>
+        <v>713090</v>
       </c>
       <c r="R42" t="n">
-        <v>7103963</v>
+        <v>7104219</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,12 +4812,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4836,32 +4842,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986813</v>
+        <v>126986824</v>
       </c>
       <c r="B43" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4871,10 +4877,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713149</v>
+        <v>712932</v>
       </c>
       <c r="R43" t="n">
-        <v>7104167</v>
+        <v>7104191</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4909,12 +4915,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4933,32 +4945,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986845</v>
+        <v>126986813</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4980,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713090</v>
+        <v>713149</v>
       </c>
       <c r="R44" t="n">
-        <v>7104219</v>
+        <v>7104167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,18 +5018,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5036,32 +5042,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986824</v>
+        <v>126986807</v>
       </c>
       <c r="B45" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5071,10 +5077,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712932</v>
+        <v>713191</v>
       </c>
       <c r="R45" t="n">
-        <v>7104191</v>
+        <v>7104098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5109,18 +5115,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126986811</v>
+        <v>126986854</v>
       </c>
       <c r="B6" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712733</v>
+        <v>713078</v>
       </c>
       <c r="R6" t="n">
-        <v>7104319</v>
+        <v>7104061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126986854</v>
+        <v>126986811</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713078</v>
+        <v>712733</v>
       </c>
       <c r="R7" t="n">
-        <v>7104061</v>
+        <v>7104319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1693,53 +1693,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126986818</v>
+        <v>126986831</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712755</v>
+        <v>712869</v>
       </c>
       <c r="R12" t="n">
-        <v>7104323</v>
+        <v>7104253</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,12 +1766,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>5 bladosetter</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1798,7 +1796,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126986831</v>
+        <v>126986849</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1833,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712869</v>
+        <v>713168</v>
       </c>
       <c r="R13" t="n">
-        <v>7104253</v>
+        <v>7104153</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,7 +1871,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>5 bladosetter</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1901,45 +1899,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126986849</v>
+        <v>126986818</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713168</v>
+        <v>712755</v>
       </c>
       <c r="R14" t="n">
-        <v>7104153</v>
+        <v>7104323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,18 +1980,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2523,45 +2523,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126986809</v>
+        <v>126986810</v>
       </c>
       <c r="B20" t="n">
-        <v>58488</v>
+        <v>91684</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208245</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712748</v>
+        <v>712728</v>
       </c>
       <c r="R20" t="n">
-        <v>7104315</v>
+        <v>7104311</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2596,12 +2599,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera på samma låga</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2620,32 +2629,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986853</v>
+        <v>126986856</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2655,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>713144</v>
+        <v>712983</v>
       </c>
       <c r="R21" t="n">
-        <v>7104068</v>
+        <v>7104024</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,32 +2726,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126986835</v>
+        <v>126986809</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>58488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2752,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>713177</v>
+        <v>712748</v>
       </c>
       <c r="R22" t="n">
-        <v>7104176</v>
+        <v>7104315</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,18 +2799,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2820,7 +2823,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126986852</v>
+        <v>126986853</v>
       </c>
       <c r="B23" t="n">
         <v>98443</v>
@@ -2855,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>713128</v>
+        <v>713144</v>
       </c>
       <c r="R23" t="n">
-        <v>7104085</v>
+        <v>7104068</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2917,7 +2920,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126986840</v>
+        <v>126986835</v>
       </c>
       <c r="B24" t="n">
         <v>98443</v>
@@ -2952,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>713097</v>
+        <v>713177</v>
       </c>
       <c r="R24" t="n">
-        <v>7104180</v>
+        <v>7104176</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2992,7 +2995,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3020,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126986810</v>
+        <v>126986852</v>
       </c>
       <c r="B25" t="n">
-        <v>91684</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,37 +3034,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712728</v>
+        <v>713128</v>
       </c>
       <c r="R25" t="n">
-        <v>7104311</v>
+        <v>7104085</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,18 +3096,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Flera på samma låga</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3126,32 +3120,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126986856</v>
+        <v>126986840</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3161,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712983</v>
+        <v>713097</v>
       </c>
       <c r="R26" t="n">
-        <v>7104024</v>
+        <v>7104180</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3199,12 +3193,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986815</v>
+        <v>126986807</v>
       </c>
       <c r="B41" t="n">
-        <v>91326</v>
+        <v>91291</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713013</v>
+        <v>713191</v>
       </c>
       <c r="R41" t="n">
-        <v>7103963</v>
+        <v>7104098</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4739,32 +4739,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986845</v>
+        <v>126986815</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713090</v>
+        <v>713013</v>
       </c>
       <c r="R42" t="n">
-        <v>7104219</v>
+        <v>7103963</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,18 +4812,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4842,32 +4836,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986824</v>
+        <v>126986813</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4877,10 +4871,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712932</v>
+        <v>713149</v>
       </c>
       <c r="R43" t="n">
-        <v>7104191</v>
+        <v>7104167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4915,18 +4909,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4945,32 +4933,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986813</v>
+        <v>126986845</v>
       </c>
       <c r="B44" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4980,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713149</v>
+        <v>713090</v>
       </c>
       <c r="R44" t="n">
-        <v>7104167</v>
+        <v>7104219</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5018,12 +5006,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5042,32 +5036,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986807</v>
+        <v>126986824</v>
       </c>
       <c r="B45" t="n">
-        <v>91291</v>
+        <v>98443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5077,10 +5071,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>713191</v>
+        <v>712932</v>
       </c>
       <c r="R45" t="n">
-        <v>7104098</v>
+        <v>7104191</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5115,12 +5109,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -1693,45 +1693,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126986831</v>
+        <v>126986818</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712869</v>
+        <v>712755</v>
       </c>
       <c r="R12" t="n">
-        <v>7104253</v>
+        <v>7104323</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,18 +1774,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>5 bladosetter</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1796,7 +1798,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126986849</v>
+        <v>126986831</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1831,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713168</v>
+        <v>712869</v>
       </c>
       <c r="R13" t="n">
-        <v>7104153</v>
+        <v>7104253</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,7 +1873,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>5 bladosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,53 +1901,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126986818</v>
+        <v>126986849</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712755</v>
+        <v>713168</v>
       </c>
       <c r="R14" t="n">
-        <v>7104323</v>
+        <v>7104153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1980,12 +1974,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986807</v>
+        <v>126986815</v>
       </c>
       <c r="B41" t="n">
-        <v>91291</v>
+        <v>91326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713191</v>
+        <v>713013</v>
       </c>
       <c r="R41" t="n">
-        <v>7104098</v>
+        <v>7103963</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4739,32 +4739,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986815</v>
+        <v>126986845</v>
       </c>
       <c r="B42" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713013</v>
+        <v>713090</v>
       </c>
       <c r="R42" t="n">
-        <v>7103963</v>
+        <v>7104219</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,12 +4812,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4836,32 +4842,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986813</v>
+        <v>126986824</v>
       </c>
       <c r="B43" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4871,10 +4877,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713149</v>
+        <v>712932</v>
       </c>
       <c r="R43" t="n">
-        <v>7104167</v>
+        <v>7104191</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4909,12 +4915,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4933,32 +4945,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986845</v>
+        <v>126986813</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4980,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713090</v>
+        <v>713149</v>
       </c>
       <c r="R44" t="n">
-        <v>7104219</v>
+        <v>7104167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,18 +5018,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5036,32 +5042,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986824</v>
+        <v>126986807</v>
       </c>
       <c r="B45" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5071,10 +5077,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712932</v>
+        <v>713191</v>
       </c>
       <c r="R45" t="n">
-        <v>7104191</v>
+        <v>7104098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5109,18 +5115,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126986829</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>126986850</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126986825</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126986844</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>126986854</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>126986811</v>
       </c>
       <c r="B7" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126986846</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126986830</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>126986832</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>126986841</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>126986818</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>126986831</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>126986849</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>126986838</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>126986836</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126986827</v>
+        <v>126986833</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,20 +2239,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712952</v>
+        <v>712891</v>
       </c>
       <c r="R17" t="n">
-        <v>7104173</v>
+        <v>7104145</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2289,7 +2285,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>30 bladrosetter, 1 blomställning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,10 +2313,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126986833</v>
+        <v>126986827</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,16 +2342,20 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712891</v>
+        <v>712952</v>
       </c>
       <c r="R18" t="n">
-        <v>7104145</v>
+        <v>7104173</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>30 bladrosetter, 1 blomställning</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,7 +2423,7 @@
         <v>126986826</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,48 +2523,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126986810</v>
+        <v>126986856</v>
       </c>
       <c r="B20" t="n">
-        <v>91684</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712728</v>
+        <v>712983</v>
       </c>
       <c r="R20" t="n">
-        <v>7104311</v>
+        <v>7104024</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2599,18 +2596,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera på samma låga</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2629,45 +2620,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986856</v>
+        <v>126986810</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>91688</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712983</v>
+        <v>712728</v>
       </c>
       <c r="R21" t="n">
-        <v>7104024</v>
+        <v>7104311</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,12 +2696,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera på samma låga</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>126986809</v>
       </c>
       <c r="B22" t="n">
-        <v>58488</v>
+        <v>58492</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>126986853</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>126986835</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>126986852</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>126986840</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126986843</v>
+        <v>126986814</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>91330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>713017</v>
+        <v>713190</v>
       </c>
       <c r="R27" t="n">
-        <v>7103987</v>
+        <v>7104098</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,18 +3296,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>15 bladrosetter, 1 blomställning</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3326,32 +3320,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126986814</v>
+        <v>126986843</v>
       </c>
       <c r="B28" t="n">
-        <v>91326</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3361,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>713190</v>
+        <v>713017</v>
       </c>
       <c r="R28" t="n">
-        <v>7104098</v>
+        <v>7103987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,12 +3393,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>15 bladrosetter, 1 blomställning</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3423,42 +3423,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126986817</v>
+        <v>126986828</v>
       </c>
       <c r="B29" t="n">
-        <v>57654</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3466,10 +3462,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712853</v>
+        <v>713049</v>
       </c>
       <c r="R29" t="n">
-        <v>7104164</v>
+        <v>7104065</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3504,12 +3500,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3528,38 +3530,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126986828</v>
+        <v>126986817</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>57658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3567,10 +3573,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>713049</v>
+        <v>712853</v>
       </c>
       <c r="R30" t="n">
-        <v>7104065</v>
+        <v>7104164</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3605,18 +3611,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>126986821</v>
       </c>
       <c r="B31" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>126986848</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>126986851</v>
       </c>
       <c r="B33" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>126987246</v>
       </c>
       <c r="B34" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>126986823</v>
       </c>
       <c r="B35" t="n">
-        <v>91527</v>
+        <v>91531</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>126986808</v>
       </c>
       <c r="B36" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>126986842</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>126986834</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126986837</v>
+        <v>126986812</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>91330</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712883</v>
+        <v>713120</v>
       </c>
       <c r="R39" t="n">
-        <v>7104261</v>
+        <v>7104213</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,18 +4515,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4545,32 +4539,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126986812</v>
+        <v>126986837</v>
       </c>
       <c r="B40" t="n">
-        <v>91326</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4580,10 +4574,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>713120</v>
+        <v>712883</v>
       </c>
       <c r="R40" t="n">
-        <v>7104213</v>
+        <v>7104261</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,12 +4612,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4642,10 +4642,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986815</v>
+        <v>126986813</v>
       </c>
       <c r="B41" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713013</v>
+        <v>713149</v>
       </c>
       <c r="R41" t="n">
-        <v>7103963</v>
+        <v>7104167</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4742,7 +4742,7 @@
         <v>126986845</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>126986824</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,10 +4945,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986813</v>
+        <v>126986815</v>
       </c>
       <c r="B44" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713149</v>
+        <v>713013</v>
       </c>
       <c r="R44" t="n">
-        <v>7104167</v>
+        <v>7103963</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5045,7 +5045,7 @@
         <v>126986807</v>
       </c>
       <c r="B45" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>126986816</v>
       </c>
       <c r="B46" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -2523,32 +2523,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126986856</v>
+        <v>126986809</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>58492</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>208245</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712983</v>
+        <v>712748</v>
       </c>
       <c r="R20" t="n">
-        <v>7104024</v>
+        <v>7104315</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,48 +2620,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986810</v>
+        <v>126986856</v>
       </c>
       <c r="B21" t="n">
-        <v>91688</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712728</v>
+        <v>712983</v>
       </c>
       <c r="R21" t="n">
-        <v>7104311</v>
+        <v>7104024</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,18 +2693,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Flera på samma låga</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2726,32 +2717,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126986809</v>
+        <v>126986853</v>
       </c>
       <c r="B22" t="n">
-        <v>58492</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2761,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712748</v>
+        <v>713144</v>
       </c>
       <c r="R22" t="n">
-        <v>7104315</v>
+        <v>7104068</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2823,7 +2814,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126986853</v>
+        <v>126986835</v>
       </c>
       <c r="B23" t="n">
         <v>98447</v>
@@ -2858,10 +2849,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>713144</v>
+        <v>713177</v>
       </c>
       <c r="R23" t="n">
-        <v>7104068</v>
+        <v>7104176</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2896,12 +2887,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2920,7 +2917,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126986835</v>
+        <v>126986852</v>
       </c>
       <c r="B24" t="n">
         <v>98447</v>
@@ -2955,10 +2952,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>713177</v>
+        <v>713128</v>
       </c>
       <c r="R24" t="n">
-        <v>7104176</v>
+        <v>7104085</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2993,18 +2990,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3023,7 +3014,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126986852</v>
+        <v>126986840</v>
       </c>
       <c r="B25" t="n">
         <v>98447</v>
@@ -3058,10 +3049,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>713128</v>
+        <v>713097</v>
       </c>
       <c r="R25" t="n">
-        <v>7104085</v>
+        <v>7104180</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,12 +3087,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3120,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126986840</v>
+        <v>126986810</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>91688</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,34 +3128,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>713097</v>
+        <v>712728</v>
       </c>
       <c r="R26" t="n">
-        <v>7104180</v>
+        <v>7104311</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>Flera på samma låga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,38 +3423,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126986828</v>
+        <v>126986817</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3462,10 +3466,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>713049</v>
+        <v>712853</v>
       </c>
       <c r="R29" t="n">
-        <v>7104065</v>
+        <v>7104164</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3500,18 +3504,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3530,42 +3528,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126986817</v>
+        <v>126986828</v>
       </c>
       <c r="B30" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3573,10 +3567,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712853</v>
+        <v>713049</v>
       </c>
       <c r="R30" t="n">
-        <v>7104164</v>
+        <v>7104065</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3611,12 +3605,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986813</v>
+        <v>126986807</v>
       </c>
       <c r="B41" t="n">
-        <v>91330</v>
+        <v>91295</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713149</v>
+        <v>713191</v>
       </c>
       <c r="R41" t="n">
-        <v>7104167</v>
+        <v>7104098</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4739,32 +4739,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986845</v>
+        <v>126986815</v>
       </c>
       <c r="B42" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713090</v>
+        <v>713013</v>
       </c>
       <c r="R42" t="n">
-        <v>7104219</v>
+        <v>7103963</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,18 +4812,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4842,32 +4836,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986824</v>
+        <v>126986813</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4877,10 +4871,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712932</v>
+        <v>713149</v>
       </c>
       <c r="R43" t="n">
-        <v>7104191</v>
+        <v>7104167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4915,18 +4909,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4945,32 +4933,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986815</v>
+        <v>126986824</v>
       </c>
       <c r="B44" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4980,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713013</v>
+        <v>712932</v>
       </c>
       <c r="R44" t="n">
-        <v>7103963</v>
+        <v>7104191</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5018,12 +5006,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5042,32 +5036,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986807</v>
+        <v>126986845</v>
       </c>
       <c r="B45" t="n">
-        <v>91295</v>
+        <v>98447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5077,10 +5071,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>713191</v>
+        <v>713090</v>
       </c>
       <c r="R45" t="n">
-        <v>7104098</v>
+        <v>7104219</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5115,12 +5109,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126986812</v>
+        <v>126986837</v>
       </c>
       <c r="B39" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>713120</v>
+        <v>712883</v>
       </c>
       <c r="R39" t="n">
-        <v>7104213</v>
+        <v>7104261</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,12 +4515,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4539,32 +4545,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126986837</v>
+        <v>126986812</v>
       </c>
       <c r="B40" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4574,10 +4580,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712883</v>
+        <v>713120</v>
       </c>
       <c r="R40" t="n">
-        <v>7104261</v>
+        <v>7104213</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4612,18 +4618,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986807</v>
+        <v>126986845</v>
       </c>
       <c r="B41" t="n">
-        <v>91295</v>
+        <v>98447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713191</v>
+        <v>713090</v>
       </c>
       <c r="R41" t="n">
-        <v>7104098</v>
+        <v>7104219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,12 +4715,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4739,32 +4745,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986815</v>
+        <v>126986807</v>
       </c>
       <c r="B42" t="n">
-        <v>91330</v>
+        <v>91295</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4774,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713013</v>
+        <v>713191</v>
       </c>
       <c r="R42" t="n">
-        <v>7103963</v>
+        <v>7104098</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4836,7 +4842,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986813</v>
+        <v>126986815</v>
       </c>
       <c r="B43" t="n">
         <v>91330</v>
@@ -4871,10 +4877,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713149</v>
+        <v>713013</v>
       </c>
       <c r="R43" t="n">
-        <v>7104167</v>
+        <v>7103963</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4933,32 +4939,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986824</v>
+        <v>126986813</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4974,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712932</v>
+        <v>713149</v>
       </c>
       <c r="R44" t="n">
-        <v>7104191</v>
+        <v>7104167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,18 +5012,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986845</v>
+        <v>126986824</v>
       </c>
       <c r="B45" t="n">
         <v>98447</v>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>713090</v>
+        <v>712932</v>
       </c>
       <c r="R45" t="n">
-        <v>7104219</v>
+        <v>7104191</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -2523,32 +2523,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126986809</v>
+        <v>126986856</v>
       </c>
       <c r="B20" t="n">
-        <v>58492</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208245</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712748</v>
+        <v>712983</v>
       </c>
       <c r="R20" t="n">
-        <v>7104315</v>
+        <v>7104024</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,45 +2620,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986856</v>
+        <v>126986810</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>91688</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712983</v>
+        <v>712728</v>
       </c>
       <c r="R21" t="n">
-        <v>7104024</v>
+        <v>7104311</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,12 +2696,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera på samma låga</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2717,32 +2726,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126986853</v>
+        <v>126986809</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>58492</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2752,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>713144</v>
+        <v>712748</v>
       </c>
       <c r="R22" t="n">
-        <v>7104068</v>
+        <v>7104315</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2814,7 +2823,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126986835</v>
+        <v>126986853</v>
       </c>
       <c r="B23" t="n">
         <v>98447</v>
@@ -2849,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>713177</v>
+        <v>713144</v>
       </c>
       <c r="R23" t="n">
-        <v>7104176</v>
+        <v>7104068</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,18 +2896,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2917,7 +2920,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126986852</v>
+        <v>126986835</v>
       </c>
       <c r="B24" t="n">
         <v>98447</v>
@@ -2952,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>713128</v>
+        <v>713177</v>
       </c>
       <c r="R24" t="n">
-        <v>7104085</v>
+        <v>7104176</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,12 +2993,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3014,7 +3023,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126986840</v>
+        <v>126986852</v>
       </c>
       <c r="B25" t="n">
         <v>98447</v>
@@ -3049,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>713097</v>
+        <v>713128</v>
       </c>
       <c r="R25" t="n">
-        <v>7104180</v>
+        <v>7104085</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,18 +3096,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3117,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126986810</v>
+        <v>126986840</v>
       </c>
       <c r="B26" t="n">
-        <v>91688</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3128,37 +3131,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712728</v>
+        <v>713097</v>
       </c>
       <c r="R26" t="n">
-        <v>7104311</v>
+        <v>7104180</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Flera på samma låga</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3528,49 +3528,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126986828</v>
+        <v>126986821</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>97325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>713049</v>
+        <v>713031</v>
       </c>
       <c r="R30" t="n">
-        <v>7104065</v>
+        <v>7104028</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3605,18 +3601,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3635,45 +3625,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126986821</v>
+        <v>126986828</v>
       </c>
       <c r="B31" t="n">
-        <v>97325</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>713031</v>
+        <v>713049</v>
       </c>
       <c r="R31" t="n">
-        <v>7104028</v>
+        <v>7104065</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3708,12 +3702,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126986837</v>
+        <v>126986812</v>
       </c>
       <c r="B39" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712883</v>
+        <v>713120</v>
       </c>
       <c r="R39" t="n">
-        <v>7104261</v>
+        <v>7104213</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,18 +4515,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4545,32 +4539,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126986812</v>
+        <v>126986837</v>
       </c>
       <c r="B40" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4580,10 +4574,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>713120</v>
+        <v>712883</v>
       </c>
       <c r="R40" t="n">
-        <v>7104213</v>
+        <v>7104261</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,12 +4612,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4745,32 +4745,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986807</v>
+        <v>126986824</v>
       </c>
       <c r="B42" t="n">
-        <v>91295</v>
+        <v>98447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713191</v>
+        <v>712932</v>
       </c>
       <c r="R42" t="n">
-        <v>7104098</v>
+        <v>7104191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4818,12 +4818,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4842,32 +4848,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986815</v>
+        <v>126986807</v>
       </c>
       <c r="B43" t="n">
-        <v>91330</v>
+        <v>91295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4877,10 +4883,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713013</v>
+        <v>713191</v>
       </c>
       <c r="R43" t="n">
-        <v>7103963</v>
+        <v>7104098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4939,7 +4945,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986813</v>
+        <v>126986815</v>
       </c>
       <c r="B44" t="n">
         <v>91330</v>
@@ -4974,10 +4980,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713149</v>
+        <v>713013</v>
       </c>
       <c r="R44" t="n">
-        <v>7104167</v>
+        <v>7103963</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5036,32 +5042,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986824</v>
+        <v>126986813</v>
       </c>
       <c r="B45" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5071,10 +5077,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712932</v>
+        <v>713149</v>
       </c>
       <c r="R45" t="n">
-        <v>7104191</v>
+        <v>7104167</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5109,18 +5115,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126986829</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>126986850</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126986825</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126986844</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126986854</v>
+        <v>126986811</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713078</v>
+        <v>712733</v>
       </c>
       <c r="R6" t="n">
-        <v>7104061</v>
+        <v>7104319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126986811</v>
+        <v>126986854</v>
       </c>
       <c r="B7" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712733</v>
+        <v>713078</v>
       </c>
       <c r="R7" t="n">
-        <v>7104319</v>
+        <v>7104061</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>126986846</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126986830</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>126986832</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>126986841</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,53 +1693,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126986818</v>
+        <v>126986831</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712755</v>
+        <v>712869</v>
       </c>
       <c r="R12" t="n">
-        <v>7104323</v>
+        <v>7104253</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,12 +1766,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>5 bladosetter</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1798,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126986831</v>
+        <v>126986849</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712869</v>
+        <v>713168</v>
       </c>
       <c r="R13" t="n">
-        <v>7104253</v>
+        <v>7104153</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,7 +1871,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>5 bladosetter</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1901,45 +1899,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126986849</v>
+        <v>126986818</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713168</v>
+        <v>712755</v>
       </c>
       <c r="R14" t="n">
-        <v>7104153</v>
+        <v>7104323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,18 +1980,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>126986838</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>126986836</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>126986833</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>126986827</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>126986826</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>126986853</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>126986835</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>126986852</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>126986840</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126986814</v>
+        <v>126986843</v>
       </c>
       <c r="B27" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>713190</v>
+        <v>713017</v>
       </c>
       <c r="R27" t="n">
-        <v>7104098</v>
+        <v>7103987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,12 +3296,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>15 bladrosetter, 1 blomställning</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3320,32 +3326,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126986843</v>
+        <v>126986814</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3355,10 +3361,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>713017</v>
+        <v>713190</v>
       </c>
       <c r="R28" t="n">
-        <v>7103987</v>
+        <v>7104098</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,18 +3399,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>15 bladrosetter, 1 blomställning</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>126986828</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>126986848</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>126986851</v>
       </c>
       <c r="B33" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>126987246</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>126986842</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>126986834</v>
       </c>
       <c r="B38" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>126986837</v>
       </c>
       <c r="B40" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986845</v>
+        <v>126986815</v>
       </c>
       <c r="B41" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713090</v>
+        <v>713013</v>
       </c>
       <c r="R41" t="n">
-        <v>7104219</v>
+        <v>7103963</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,18 +4715,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4745,32 +4739,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986824</v>
+        <v>126986813</v>
       </c>
       <c r="B42" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4774,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712932</v>
+        <v>713149</v>
       </c>
       <c r="R42" t="n">
-        <v>7104191</v>
+        <v>7104167</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4818,18 +4812,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4945,32 +4933,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986815</v>
+        <v>126986845</v>
       </c>
       <c r="B44" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4980,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713013</v>
+        <v>713090</v>
       </c>
       <c r="R44" t="n">
-        <v>7103963</v>
+        <v>7104219</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5018,12 +5006,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5042,32 +5036,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986813</v>
+        <v>126986824</v>
       </c>
       <c r="B45" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5077,10 +5071,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>713149</v>
+        <v>712932</v>
       </c>
       <c r="R45" t="n">
-        <v>7104167</v>
+        <v>7104191</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5115,12 +5109,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -2523,32 +2523,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126986856</v>
+        <v>126986809</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>58492</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>208245</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712983</v>
+        <v>712748</v>
       </c>
       <c r="R20" t="n">
-        <v>7104024</v>
+        <v>7104315</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,48 +2620,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986810</v>
+        <v>126986856</v>
       </c>
       <c r="B21" t="n">
-        <v>91688</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712728</v>
+        <v>712983</v>
       </c>
       <c r="R21" t="n">
-        <v>7104311</v>
+        <v>7104024</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,18 +2693,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Flera på samma låga</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2726,45 +2717,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126986809</v>
+        <v>126986810</v>
       </c>
       <c r="B22" t="n">
-        <v>58492</v>
+        <v>91688</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712748</v>
+        <v>712728</v>
       </c>
       <c r="R22" t="n">
-        <v>7104315</v>
+        <v>7104311</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2799,12 +2793,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flera på samma låga</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126986843</v>
+        <v>126986814</v>
       </c>
       <c r="B27" t="n">
-        <v>98448</v>
+        <v>91330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>713017</v>
+        <v>713190</v>
       </c>
       <c r="R27" t="n">
-        <v>7103987</v>
+        <v>7104098</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,18 +3296,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>15 bladrosetter, 1 blomställning</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3326,32 +3320,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126986814</v>
+        <v>126986843</v>
       </c>
       <c r="B28" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3361,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>713190</v>
+        <v>713017</v>
       </c>
       <c r="R28" t="n">
-        <v>7104098</v>
+        <v>7103987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,12 +3393,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>15 bladrosetter, 1 blomställning</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3423,42 +3423,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126986817</v>
+        <v>126986828</v>
       </c>
       <c r="B29" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3466,10 +3462,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712853</v>
+        <v>713049</v>
       </c>
       <c r="R29" t="n">
-        <v>7104164</v>
+        <v>7104065</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3504,12 +3500,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3625,38 +3627,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126986828</v>
+        <v>126986817</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>57658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3664,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>713049</v>
+        <v>712853</v>
       </c>
       <c r="R31" t="n">
-        <v>7104065</v>
+        <v>7104164</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,18 +3708,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126986812</v>
+        <v>126986837</v>
       </c>
       <c r="B39" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>713120</v>
+        <v>712883</v>
       </c>
       <c r="R39" t="n">
-        <v>7104213</v>
+        <v>7104261</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,12 +4515,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4539,32 +4545,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126986837</v>
+        <v>126986812</v>
       </c>
       <c r="B40" t="n">
-        <v>98448</v>
+        <v>91330</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4574,10 +4580,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712883</v>
+        <v>713120</v>
       </c>
       <c r="R40" t="n">
-        <v>7104261</v>
+        <v>7104213</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4612,18 +4618,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986815</v>
+        <v>126986845</v>
       </c>
       <c r="B41" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713013</v>
+        <v>713090</v>
       </c>
       <c r="R41" t="n">
-        <v>7103963</v>
+        <v>7104219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,12 +4715,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4739,32 +4745,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986813</v>
+        <v>126986824</v>
       </c>
       <c r="B42" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4774,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713149</v>
+        <v>712932</v>
       </c>
       <c r="R42" t="n">
-        <v>7104167</v>
+        <v>7104191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,12 +4818,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4836,32 +4848,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986807</v>
+        <v>126986815</v>
       </c>
       <c r="B43" t="n">
-        <v>91295</v>
+        <v>91330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4871,10 +4883,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713191</v>
+        <v>713013</v>
       </c>
       <c r="R43" t="n">
-        <v>7104098</v>
+        <v>7103963</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4933,32 +4945,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986845</v>
+        <v>126986813</v>
       </c>
       <c r="B44" t="n">
-        <v>98448</v>
+        <v>91330</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4980,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713090</v>
+        <v>713149</v>
       </c>
       <c r="R44" t="n">
-        <v>7104219</v>
+        <v>7104167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,18 +5018,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5036,32 +5042,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986824</v>
+        <v>126986807</v>
       </c>
       <c r="B45" t="n">
-        <v>98448</v>
+        <v>91295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5071,10 +5077,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712932</v>
+        <v>713191</v>
       </c>
       <c r="R45" t="n">
-        <v>7104191</v>
+        <v>7104098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5109,18 +5115,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126986829</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>126986850</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126986825</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126986844</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>126986811</v>
       </c>
       <c r="B6" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>126986854</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126986846</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126986830</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>126986832</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>126986841</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,45 +1693,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126986831</v>
+        <v>126986818</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712869</v>
+        <v>712755</v>
       </c>
       <c r="R12" t="n">
-        <v>7104253</v>
+        <v>7104323</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,18 +1774,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>5 bladosetter</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1796,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126986849</v>
+        <v>126986831</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1831,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713168</v>
+        <v>712869</v>
       </c>
       <c r="R13" t="n">
-        <v>7104153</v>
+        <v>7104253</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,7 +1873,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>5 bladosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,53 +1901,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126986818</v>
+        <v>126986849</v>
       </c>
       <c r="B14" t="n">
-        <v>57658</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712755</v>
+        <v>713168</v>
       </c>
       <c r="R14" t="n">
-        <v>7104323</v>
+        <v>7104153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1980,12 +1974,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>126986838</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>126986836</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>126986833</v>
       </c>
       <c r="B17" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>126986827</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>126986826</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126986809</v>
+        <v>126986856</v>
       </c>
       <c r="B20" t="n">
-        <v>58492</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208245</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712748</v>
+        <v>712983</v>
       </c>
       <c r="R20" t="n">
-        <v>7104315</v>
+        <v>7104024</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,45 +2620,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986856</v>
+        <v>126986810</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>91690</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712983</v>
+        <v>712728</v>
       </c>
       <c r="R21" t="n">
-        <v>7104024</v>
+        <v>7104311</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,12 +2696,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera på samma låga</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2717,48 +2726,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126986810</v>
+        <v>126986809</v>
       </c>
       <c r="B22" t="n">
-        <v>91688</v>
+        <v>58494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>208245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712728</v>
+        <v>712748</v>
       </c>
       <c r="R22" t="n">
-        <v>7104311</v>
+        <v>7104315</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2793,18 +2799,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Flera på samma låga</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>126986853</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>126986835</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>126986852</v>
       </c>
       <c r="B25" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>126986840</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>126986814</v>
       </c>
       <c r="B27" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>126986843</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>126986828</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>126986821</v>
       </c>
       <c r="B30" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>126986817</v>
       </c>
       <c r="B31" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>126986848</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>126986851</v>
       </c>
       <c r="B33" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>126987246</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>126986823</v>
       </c>
       <c r="B35" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4139,32 +4139,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126986808</v>
+        <v>126986842</v>
       </c>
       <c r="B36" t="n">
-        <v>91295</v>
+        <v>98450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712922</v>
+        <v>713010</v>
       </c>
       <c r="R36" t="n">
-        <v>7104137</v>
+        <v>7104171</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4212,12 +4212,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4236,10 +4242,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126986842</v>
+        <v>126986834</v>
       </c>
       <c r="B37" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4271,10 +4277,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>713010</v>
+        <v>713087</v>
       </c>
       <c r="R37" t="n">
-        <v>7104171</v>
+        <v>7104233</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4311,7 +4317,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4339,32 +4345,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126986834</v>
+        <v>126986808</v>
       </c>
       <c r="B38" t="n">
-        <v>98448</v>
+        <v>91297</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4374,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>713087</v>
+        <v>712922</v>
       </c>
       <c r="R38" t="n">
-        <v>7104233</v>
+        <v>7104137</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4412,18 +4418,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126986837</v>
+        <v>126986812</v>
       </c>
       <c r="B39" t="n">
-        <v>98448</v>
+        <v>91332</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712883</v>
+        <v>713120</v>
       </c>
       <c r="R39" t="n">
-        <v>7104261</v>
+        <v>7104213</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,18 +4515,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4545,32 +4539,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126986812</v>
+        <v>126986837</v>
       </c>
       <c r="B40" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4580,10 +4574,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>713120</v>
+        <v>712883</v>
       </c>
       <c r="R40" t="n">
-        <v>7104213</v>
+        <v>7104261</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,12 +4612,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4645,7 +4645,7 @@
         <v>126986845</v>
       </c>
       <c r="B41" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>126986824</v>
       </c>
       <c r="B42" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>126986815</v>
       </c>
       <c r="B43" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>126986813</v>
       </c>
       <c r="B44" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>126986807</v>
       </c>
       <c r="B45" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>126986816</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126986811</v>
+        <v>126986854</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712733</v>
+        <v>713078</v>
       </c>
       <c r="R6" t="n">
-        <v>7104319</v>
+        <v>7104061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126986854</v>
+        <v>126986811</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713078</v>
+        <v>712733</v>
       </c>
       <c r="R7" t="n">
-        <v>7104061</v>
+        <v>7104319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2620,48 +2620,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986810</v>
+        <v>126986809</v>
       </c>
       <c r="B21" t="n">
-        <v>91690</v>
+        <v>58494</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>208245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712728</v>
+        <v>712748</v>
       </c>
       <c r="R21" t="n">
-        <v>7104311</v>
+        <v>7104315</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,18 +2693,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Flera på samma låga</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2726,45 +2717,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126986809</v>
+        <v>126986810</v>
       </c>
       <c r="B22" t="n">
-        <v>58494</v>
+        <v>91690</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712748</v>
+        <v>712728</v>
       </c>
       <c r="R22" t="n">
-        <v>7104315</v>
+        <v>7104311</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2799,12 +2793,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flera på samma låga</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126986814</v>
+        <v>126986843</v>
       </c>
       <c r="B27" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>713190</v>
+        <v>713017</v>
       </c>
       <c r="R27" t="n">
-        <v>7104098</v>
+        <v>7103987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,12 +3296,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>15 bladrosetter, 1 blomställning</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3320,32 +3326,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126986843</v>
+        <v>126986814</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3355,10 +3361,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>713017</v>
+        <v>713190</v>
       </c>
       <c r="R28" t="n">
-        <v>7103987</v>
+        <v>7104098</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,18 +3399,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>15 bladrosetter, 1 blomställning</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3423,38 +3423,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126986828</v>
+        <v>126986817</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3462,10 +3466,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>713049</v>
+        <v>712853</v>
       </c>
       <c r="R29" t="n">
-        <v>7104065</v>
+        <v>7104164</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3500,18 +3504,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3627,42 +3625,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126986817</v>
+        <v>126986828</v>
       </c>
       <c r="B31" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3670,10 +3664,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712853</v>
+        <v>713049</v>
       </c>
       <c r="R31" t="n">
-        <v>7104164</v>
+        <v>7104065</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3708,12 +3702,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986845</v>
+        <v>126986815</v>
       </c>
       <c r="B41" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713090</v>
+        <v>713013</v>
       </c>
       <c r="R41" t="n">
-        <v>7104219</v>
+        <v>7103963</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,18 +4715,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4745,32 +4739,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986824</v>
+        <v>126986813</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4774,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712932</v>
+        <v>713149</v>
       </c>
       <c r="R42" t="n">
-        <v>7104191</v>
+        <v>7104167</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4818,18 +4812,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4848,32 +4836,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986815</v>
+        <v>126986807</v>
       </c>
       <c r="B43" t="n">
-        <v>91332</v>
+        <v>91297</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4883,10 +4871,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713013</v>
+        <v>713191</v>
       </c>
       <c r="R43" t="n">
-        <v>7103963</v>
+        <v>7104098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4945,32 +4933,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986813</v>
+        <v>126986845</v>
       </c>
       <c r="B44" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4980,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713149</v>
+        <v>713090</v>
       </c>
       <c r="R44" t="n">
-        <v>7104167</v>
+        <v>7104219</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5018,12 +5006,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5042,32 +5036,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986807</v>
+        <v>126986824</v>
       </c>
       <c r="B45" t="n">
-        <v>91297</v>
+        <v>98450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5077,10 +5071,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>713191</v>
+        <v>712932</v>
       </c>
       <c r="R45" t="n">
-        <v>7104098</v>
+        <v>7104191</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5115,12 +5109,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -4139,32 +4139,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126986842</v>
+        <v>126986808</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>91297</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>713010</v>
+        <v>712922</v>
       </c>
       <c r="R36" t="n">
-        <v>7104171</v>
+        <v>7104137</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4212,18 +4212,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4242,7 +4236,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126986834</v>
+        <v>126986842</v>
       </c>
       <c r="B37" t="n">
         <v>98450</v>
@@ -4277,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>713087</v>
+        <v>713010</v>
       </c>
       <c r="R37" t="n">
-        <v>7104233</v>
+        <v>7104171</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,7 +4311,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>30 bladrosetter</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4345,32 +4339,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126986808</v>
+        <v>126986834</v>
       </c>
       <c r="B38" t="n">
-        <v>91297</v>
+        <v>98450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4374,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712922</v>
+        <v>713087</v>
       </c>
       <c r="R38" t="n">
-        <v>7104137</v>
+        <v>7104233</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4418,12 +4412,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4836,32 +4836,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986807</v>
+        <v>126986845</v>
       </c>
       <c r="B43" t="n">
-        <v>91297</v>
+        <v>98450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713191</v>
+        <v>713090</v>
       </c>
       <c r="R43" t="n">
-        <v>7104098</v>
+        <v>7104219</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4909,12 +4909,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4933,7 +4939,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986845</v>
+        <v>126986824</v>
       </c>
       <c r="B44" t="n">
         <v>98450</v>
@@ -4968,10 +4974,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713090</v>
+        <v>712932</v>
       </c>
       <c r="R44" t="n">
-        <v>7104219</v>
+        <v>7104191</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5008,7 +5014,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5036,32 +5042,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126986824</v>
+        <v>126986807</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>91297</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5071,10 +5077,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712932</v>
+        <v>713191</v>
       </c>
       <c r="R45" t="n">
-        <v>7104191</v>
+        <v>7104098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5109,18 +5115,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 261-2024 artfynd.xlsx
+++ b/artfynd/A 261-2024 artfynd.xlsx
@@ -2620,32 +2620,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126986809</v>
+        <v>126986853</v>
       </c>
       <c r="B21" t="n">
-        <v>58494</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712748</v>
+        <v>713144</v>
       </c>
       <c r="R21" t="n">
-        <v>7104315</v>
+        <v>7104068</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126986810</v>
+        <v>126986835</v>
       </c>
       <c r="B22" t="n">
-        <v>91690</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2728,37 +2728,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712728</v>
+        <v>713177</v>
       </c>
       <c r="R22" t="n">
-        <v>7104311</v>
+        <v>7104176</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2795,7 +2792,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flera på samma låga</t>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2823,7 +2820,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126986853</v>
+        <v>126986852</v>
       </c>
       <c r="B23" t="n">
         <v>98450</v>
@@ -2858,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>713144</v>
+        <v>713128</v>
       </c>
       <c r="R23" t="n">
-        <v>7104068</v>
+        <v>7104085</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,7 +2917,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126986835</v>
+        <v>126986840</v>
       </c>
       <c r="B24" t="n">
         <v>98450</v>
@@ -2955,10 +2952,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>713177</v>
+        <v>713097</v>
       </c>
       <c r="R24" t="n">
-        <v>7104176</v>
+        <v>7104180</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2995,7 +2992,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>30 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3023,10 +3020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126986852</v>
+        <v>126986810</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>91690</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,34 +3031,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>713128</v>
+        <v>712728</v>
       </c>
       <c r="R25" t="n">
-        <v>7104085</v>
+        <v>7104311</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,12 +3096,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Flera på samma låga</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3120,32 +3126,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126986840</v>
+        <v>126986809</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>58494</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3161,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>713097</v>
+        <v>712748</v>
       </c>
       <c r="R26" t="n">
-        <v>7104180</v>
+        <v>7104315</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,18 +3199,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126986843</v>
+        <v>126986814</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>713017</v>
+        <v>713190</v>
       </c>
       <c r="R27" t="n">
-        <v>7103987</v>
+        <v>7104098</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,18 +3296,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>15 bladrosetter, 1 blomställning</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3326,32 +3320,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126986814</v>
+        <v>126986843</v>
       </c>
       <c r="B28" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3361,10 +3355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>713190</v>
+        <v>713017</v>
       </c>
       <c r="R28" t="n">
-        <v>7104098</v>
+        <v>7103987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,12 +3393,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>15 bladrosetter, 1 blomställning</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3528,45 +3528,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126986821</v>
+        <v>126986828</v>
       </c>
       <c r="B30" t="n">
-        <v>97327</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>713031</v>
+        <v>713049</v>
       </c>
       <c r="R30" t="n">
-        <v>7104028</v>
+        <v>7104065</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,12 +3605,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3625,49 +3635,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126986828</v>
+        <v>126986821</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>97327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kråkdalsliden, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>713049</v>
+        <v>713031</v>
       </c>
       <c r="R31" t="n">
-        <v>7104065</v>
+        <v>7104028</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,18 +3708,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4642,32 +4642,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126986815</v>
+        <v>126986845</v>
       </c>
       <c r="B41" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713013</v>
+        <v>713090</v>
       </c>
       <c r="R41" t="n">
-        <v>7103963</v>
+        <v>7104219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,12 +4715,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4739,32 +4745,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126986813</v>
+        <v>126986824</v>
       </c>
       <c r="B42" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4774,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713149</v>
+        <v>712932</v>
       </c>
       <c r="R42" t="n">
-        <v>7104167</v>
+        <v>7104191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,12 +4818,18 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4836,32 +4848,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126986845</v>
+        <v>126986815</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4871,10 +4883,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713090</v>
+        <v>713013</v>
       </c>
       <c r="R43" t="n">
-        <v>7104219</v>
+        <v>7103963</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4909,18 +4921,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, 3 blomställningar</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4939,32 +4945,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126986824</v>
+        <v>126986813</v>
       </c>
       <c r="B44" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4974,10 +4980,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712932</v>
+        <v>713149</v>
       </c>
       <c r="R44" t="n">
-        <v>7104191</v>
+        <v>7104167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5012,18 +5018,12 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
